--- a/src/test/resources/TestData/MrYoda.xlsx
+++ b/src/test/resources/TestData/MrYoda.xlsx
@@ -474,7 +474,7 @@
         <v>123456</v>
       </c>
       <c r="C2" t="str">
-        <v>Bone Profile -1</v>
+        <v>Anemia Panel</v>
       </c>
       <c r="D2" t="str">
         <v>Ranjith kumar A</v>
@@ -533,7 +533,7 @@
         <v>123456</v>
       </c>
       <c r="C3" t="str">
-        <v>Bone Profile -1</v>
+        <v>Anemia Panel,Bone Profile -1</v>
       </c>
       <c r="D3" t="str">
         <v>Ranjith kumar A</v>
@@ -711,7 +711,7 @@
         <v>123456</v>
       </c>
       <c r="C6" t="str">
-        <v>Bone Profile -1</v>
+        <v>Anemia Panel</v>
       </c>
       <c r="D6" t="str">
         <v>Test</v>
@@ -770,7 +770,7 @@
         <v>123456</v>
       </c>
       <c r="C7" t="str">
-        <v>Bone Profile -1</v>
+        <v>Anemia Panel</v>
       </c>
       <c r="D7" t="str">
         <v>Test</v>
@@ -988,7 +988,7 @@
         <v>123456</v>
       </c>
       <c r="C11" t="str">
-        <v>Bone Profile -1</v>
+        <v>Anemia Panel</v>
       </c>
       <c r="D11" t="str">
         <v>Ranjith kumar A</v>

--- a/src/test/resources/TestData/MrYoda.xlsx
+++ b/src/test/resources/TestData/MrYoda.xlsx
@@ -474,7 +474,7 @@
         <v>123456</v>
       </c>
       <c r="C2" t="str">
-        <v>Anemia Panel</v>
+        <v>Bone Profile -1</v>
       </c>
       <c r="D2" t="str">
         <v>Ranjith kumar A</v>
@@ -533,7 +533,7 @@
         <v>123456</v>
       </c>
       <c r="C3" t="str">
-        <v>Anemia Panel,Bone Profile -1</v>
+        <v>Master Health Checkup,Bone Profile -1</v>
       </c>
       <c r="D3" t="str">
         <v>Ranjith kumar A</v>
@@ -592,7 +592,7 @@
         <v>123456</v>
       </c>
       <c r="C4" t="str">
-        <v>Anemia Panel,Bone Profile -1</v>
+        <v>Master Health Checkup,Bone Profile -1</v>
       </c>
       <c r="D4" t="str">
         <v>Ranjith kumar A</v>
@@ -651,7 +651,7 @@
         <v>123456</v>
       </c>
       <c r="C5" t="str">
-        <v>Anemia Panel,Bone Profile -1</v>
+        <v>Master Health Checkup,Bone Profile -1</v>
       </c>
       <c r="D5" t="str">
         <v>Ranjith kumar A</v>
@@ -711,7 +711,7 @@
         <v>123456</v>
       </c>
       <c r="C6" t="str">
-        <v>Anemia Panel</v>
+        <v>Master Health Checkup</v>
       </c>
       <c r="D6" t="str">
         <v>Test</v>
@@ -770,7 +770,7 @@
         <v>123456</v>
       </c>
       <c r="C7" t="str">
-        <v>Anemia Panel</v>
+        <v>Master Health Checkup</v>
       </c>
       <c r="D7" t="str">
         <v>Test</v>
@@ -829,7 +829,7 @@
         <v>123456</v>
       </c>
       <c r="C8" t="str">
-        <v>Anemia Panel,Bone Profile -1</v>
+        <v>Master Health Checkup,Bone Profile -1</v>
       </c>
       <c r="D8" t="str">
         <v>Test</v>
@@ -888,7 +888,7 @@
         <v>123456</v>
       </c>
       <c r="C9" t="str">
-        <v>Anemia Panel,Bone Profile -1</v>
+        <v>Master Health Checkup,Bone Profile -1</v>
       </c>
       <c r="D9" t="str">
         <v>Test</v>
@@ -988,7 +988,7 @@
         <v>123456</v>
       </c>
       <c r="C11" t="str">
-        <v>Anemia Panel</v>
+        <v>Master Health Checkup</v>
       </c>
       <c r="D11" t="str">
         <v>Ranjith kumar A</v>
